--- a/AAII_Financials/Yearly/G_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/G_YR_FIN.xlsx
@@ -3023,10 +3023,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>413400</v>
+        <v>409600</v>
       </c>
       <c r="E59" s="3">
-        <v>203600</v>
+        <v>199700</v>
       </c>
       <c r="F59" s="3">
         <v>190600</v>
